--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_BISON_COW.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_BISON_COW.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,8 +61,19 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002F1B0F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -94,8 +105,28 @@
         <fgColor rgb="004F2D1D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B301B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFE5D7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -118,11 +149,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C58F61"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C58F61"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C58F61"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C58F61"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -175,6 +220,45 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -569,448 +653,448 @@
   <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="14" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="14" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="14" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="20" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="20" bestFit="1" customWidth="1" style="7" min="6" max="6"/>
-    <col width="28" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="14" bestFit="1" customWidth="1" style="7" min="8" max="8"/>
-    <col width="14" bestFit="1" customWidth="1" style="7" min="9" max="9"/>
-    <col width="14" bestFit="1" customWidth="1" style="7" min="10" max="10"/>
-    <col width="20" bestFit="1" customWidth="1" style="7" min="11" max="11"/>
-    <col width="36" bestFit="1" customWidth="1" style="9" min="12" max="12"/>
-    <col width="20" bestFit="1" customWidth="1" style="7" min="13" max="13"/>
-    <col width="20" bestFit="1" customWidth="1" style="7" min="14" max="14"/>
-    <col width="36" customWidth="1" style="7" min="15" max="15"/>
-    <col width="36" customWidth="1" style="7" min="16" max="16"/>
+    <col width="20" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="10" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="10" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="10" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
+    <col width="14" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="14" bestFit="1" customWidth="1" style="7" min="6" max="6"/>
+    <col width="20" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="10" bestFit="1" customWidth="1" style="7" min="8" max="8"/>
+    <col width="10" bestFit="1" customWidth="1" style="7" min="9" max="9"/>
+    <col width="10" bestFit="1" customWidth="1" style="7" min="10" max="10"/>
+    <col width="14" bestFit="1" customWidth="1" style="7" min="11" max="11"/>
+    <col width="24" bestFit="1" customWidth="1" style="9" min="12" max="12"/>
+    <col width="14" bestFit="1" customWidth="1" style="7" min="13" max="13"/>
+    <col width="14" bestFit="1" customWidth="1" style="7" min="14" max="14"/>
+    <col width="24" customWidth="1" style="7" min="15" max="15"/>
+    <col width="24" customWidth="1" style="7" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" s="7">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="7">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>2026 BISON COW</t>
         </is>
       </c>
       <c r="K1" s="6" t="n"/>
     </row>
-    <row r="2" ht="24" customHeight="1" s="7"/>
+    <row r="2" ht="40" customHeight="1" s="7"/>
     <row r="3" ht="60" customHeight="1" s="7">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Hunt Name</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Hunt Code</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>Hunt Type</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="23" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t>Res</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="23" t="inlineStr">
         <is>
           <t>Non-Res</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t>Harvest Prior Year</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t>Percent Harvest Success (previous hunting season)</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="M3" s="23" t="inlineStr">
         <is>
           <t>Average Harvest Age</t>
         </is>
       </c>
-      <c r="N3" s="12" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t>Average Days Hunted</t>
         </is>
       </c>
-      <c r="O3" s="12" t="inlineStr">
+      <c r="O3" s="23" t="inlineStr">
         <is>
           <t>Average Age Harvested (previous hunting season)</t>
         </is>
       </c>
-      <c r="P3" s="12" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" s="7">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Henry Mtns</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>BI6505</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Cow Only</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>Bison</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>Dec 9 2026 - Dec 20 2026</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="29" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I4" s="16" t="n">
+      <c r="I4" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="29" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="K4" s="28" t="n">
         <v>2025</v>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="29" t="inlineStr">
         <is>
           <t>78.6</t>
         </is>
       </c>
-      <c r="M4" s="17" t="n"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="29" t="n"/>
+      <c r="N4" s="29" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O4" s="17" t="inlineStr"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="29" t="inlineStr"/>
+      <c r="P4" s="29" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" s="7">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>Henry Mtns</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>BI6506</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>Cow Only</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>Bison</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t>Dec 23, 2026 - Jan 3, 2027</t>
         </is>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="J5" s="31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="K5" s="30" t="n">
         <v>2025</v>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="31" t="inlineStr">
         <is>
           <t>93.1</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="31" t="n"/>
+      <c r="N5" s="31" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="O5" s="17" t="inlineStr"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="31" t="inlineStr"/>
+      <c r="P5" s="31" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" s="7">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Book Cliffs, Little Creek/South</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>BI6529</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>Cow Only</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>Bison</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Oct 17 2026 - Oct 27 2026</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I6" s="16" t="n">
+      <c r="I6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="29" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="28" t="n">
         <v>2025</v>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="29" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="M6" s="29" t="n"/>
+      <c r="N6" s="29" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr"/>
+      <c r="P6" s="29" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Book Cliffs, Bitter Creek</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>BI6536</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>Cow Only</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Bison</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>Nov 14 2026 - Nov 29 2026</t>
         </is>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="30" t="n">
         <v>2025</v>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="31" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="M7" s="17" t="n"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="31" t="n"/>
+      <c r="N7" s="31" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr"/>
+      <c r="P7" s="31" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="7">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Henry Mtns</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>BI6539</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Cow Only</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Bison</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>Jan 6 - 17, 2027</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="K8" s="17" t="n"/>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="17" t="n"/>
-      <c r="N8" s="17" t="n"/>
-      <c r="O8" s="17" t="n"/>
-      <c r="P8" s="17" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="29" t="n"/>
+      <c r="M8" s="29" t="n"/>
+      <c r="N8" s="29" t="n"/>
+      <c r="O8" s="29" t="n"/>
+      <c r="P8" s="29" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:P8"/>
@@ -1018,9 +1102,9 @@
     <mergeCell ref="K1:N1"/>
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.45" bottom="0.35" header="0.15" footer="0.15"/>
-  <pageSetup orientation="landscape" fitToHeight="0"/>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Georgia,Bold"&amp;12 2026 BISON COW</oddHeader>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
